--- a/SchoolOnboardingTemplate.xlsx
+++ b/SchoolOnboardingTemplate.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="259" documentId="11_63A18EA0B7CBAF34536809B7D3B5B958FBB2D180" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17C4273E-5AC3-4C32-99CF-EAB90792A49F}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_E32A8A1067A7EB7FB30A1DB7D3B5B958FBB2CF77" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C414A4F8-97F9-446E-BC94-4C39092B3C42}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1011" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="890" uniqueCount="133">
   <si>
     <t xml:space="preserve">  HOW TO FILL IN THIS TEMPLATE</t>
   </si>
@@ -200,13 +200,43 @@
     <t>Assigned Class</t>
   </si>
   <si>
+    <t>Ms Sunshine</t>
+  </si>
+  <si>
+    <t>teacher1@myschool.com</t>
+  </si>
+  <si>
+    <t>teacher</t>
+  </si>
+  <si>
+    <t>Sunshine Bunnies</t>
+  </si>
+  <si>
+    <t>Mr Rainbow</t>
+  </si>
+  <si>
+    <t>teacher2@myschool.com</t>
+  </si>
+  <si>
+    <t>Rainbow Cubs</t>
+  </si>
+  <si>
+    <t>View Only</t>
+  </si>
+  <si>
+    <t>viewer@myschool.com</t>
+  </si>
+  <si>
+    <t>viewer</t>
+  </si>
+  <si>
     <t xml:space="preserve">  STUDENTS / LEARNERS</t>
   </si>
   <si>
     <t xml:space="preserve">  Add one row per learner. Class Name must match exactly what is written on the Staff sheet.</t>
   </si>
   <si>
-    <t xml:space="preserve">  Child ID can be provided for your internal reference. Emergency Contact 1 (name + number) is required. You can add up to 4 emergency contacts per learner. EC1 email and medical aid fields are optional unless your process requires them.</t>
+    <t xml:space="preserve">  Child ID can be provided for your internal reference. Emergency Contact 1 (name + number) is required. You can add up to 4 emergency contacts per learner. EC1/EC2 email and medical aid fields are optional unless your process requires them.</t>
   </si>
   <si>
     <t>Child ID</t>
@@ -239,6 +269,9 @@
     <t>EC2 Number</t>
   </si>
   <si>
+    <t>EC2 Email</t>
+  </si>
+  <si>
     <t>EC3 Name</t>
   </si>
   <si>
@@ -272,458 +305,125 @@
     <t>Doctor Contact</t>
   </si>
   <si>
+    <t>CH-001</t>
+  </si>
+  <si>
+    <t>Liam</t>
+  </si>
+  <si>
+    <t>Smith</t>
+  </si>
+  <si>
+    <t>Peanuts</t>
+  </si>
+  <si>
+    <t>Sarah Smith</t>
+  </si>
+  <si>
+    <t>+27821234001</t>
+  </si>
+  <si>
+    <t>sarah@example.com</t>
+  </si>
+  <si>
     <t>Discovery</t>
   </si>
   <si>
+    <t>Classic Smart</t>
+  </si>
+  <si>
+    <t>D12345</t>
+  </si>
+  <si>
+    <t>8201015009087</t>
+  </si>
+  <si>
+    <t>01</t>
+  </si>
+  <si>
     <t>Dr Patel +27112223333</t>
   </si>
   <si>
+    <t>CH-002</t>
+  </si>
+  <si>
+    <t>Emma</t>
+  </si>
+  <si>
+    <t>Johnson</t>
+  </si>
+  <si>
+    <t>No known allergies</t>
+  </si>
+  <si>
+    <t>Tom Johnson</t>
+  </si>
+  <si>
+    <t>+27821234002</t>
+  </si>
+  <si>
+    <t>CH-003</t>
+  </si>
+  <si>
+    <t>Sophia</t>
+  </si>
+  <si>
+    <t>Wilson</t>
+  </si>
+  <si>
+    <t>Dairy</t>
+  </si>
+  <si>
+    <t>Mark Wilson</t>
+  </si>
+  <si>
+    <t>+27821234006</t>
+  </si>
+  <si>
+    <t>mark@example.com</t>
+  </si>
+  <si>
+    <t>Ann Wilson</t>
+  </si>
+  <si>
+    <t>+27821234099</t>
+  </si>
+  <si>
+    <t>ann@example.com</t>
+  </si>
+  <si>
+    <t>Jane Wilson</t>
+  </si>
+  <si>
+    <t>+27825551111</t>
+  </si>
+  <si>
+    <t>Luke Wilson</t>
+  </si>
+  <si>
+    <t>+27825552222</t>
+  </si>
+  <si>
     <t>Bonitas</t>
   </si>
   <si>
-    <t xml:space="preserve">Zailey </t>
-  </si>
-  <si>
-    <t>Booysen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sion Wilhelm </t>
-  </si>
-  <si>
-    <t>Joubert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lana </t>
-  </si>
-  <si>
-    <t>Steyn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wynand Jacobus Van Der Merwe </t>
-  </si>
-  <si>
-    <t>Geen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aksel Moskou </t>
-  </si>
-  <si>
-    <t>Potgieter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lehan André </t>
-  </si>
-  <si>
-    <t>Volschenk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leilah Gabriella </t>
-  </si>
-  <si>
-    <t>Koen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zion Travis </t>
-  </si>
-  <si>
-    <t>Lynch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jackson </t>
-  </si>
-  <si>
-    <t>Burnard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Janno (Johan Johachim) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zian </t>
-  </si>
-  <si>
-    <t>Swanepoel</t>
-  </si>
-  <si>
-    <t>18.10.2024</t>
-  </si>
-  <si>
-    <t>Greenhill</t>
-  </si>
-  <si>
-    <t>Beane (Ouer)</t>
-  </si>
-  <si>
-    <t>beanebooysen@gmail.com</t>
-  </si>
-  <si>
-    <t>Fjjuba@gmail.com</t>
-  </si>
-  <si>
-    <t>Jolinda@bmpsolutions.co.za</t>
-  </si>
-  <si>
-    <t>zandre@zs-law.co.za</t>
-  </si>
-  <si>
-    <t>marycebeyers135@gmail.com</t>
-  </si>
-  <si>
-    <t>hendri@cmv.co.za</t>
-  </si>
-  <si>
-    <t>Jaco@scdsa.co.za</t>
-  </si>
-  <si>
-    <t>Rochelle.roos@icloud.com</t>
-  </si>
-  <si>
-    <t>Chantefritz97@gmail.com</t>
-  </si>
-  <si>
-    <t>Melissa@medissage.co.za</t>
-  </si>
-  <si>
-    <t>lehandre.nieuwoudt@gmail.com</t>
-  </si>
-  <si>
-    <t>talitha@aircube.co.za</t>
-  </si>
-  <si>
-    <t>CJ (ouer)</t>
-  </si>
-  <si>
-    <t>0836598703</t>
-  </si>
-  <si>
-    <t>0723948225</t>
-  </si>
-  <si>
-    <t>0825617003</t>
-  </si>
-  <si>
-    <t>Trinké (ouma)</t>
-  </si>
-  <si>
-    <t>Medshield</t>
-  </si>
-  <si>
-    <t>Momentum Health</t>
-  </si>
-  <si>
-    <t>Momentum</t>
-  </si>
-  <si>
-    <t>Medihelp</t>
-  </si>
-  <si>
-    <t>Bestmed</t>
-  </si>
-  <si>
-    <t>Medivalue Prime</t>
-  </si>
-  <si>
-    <t>Essential Core</t>
-  </si>
-  <si>
-    <t>Custom</t>
-  </si>
-  <si>
-    <t>Classic Saver</t>
-  </si>
-  <si>
-    <t>MedPrime Elect</t>
-  </si>
-  <si>
-    <t>Prime 1</t>
-  </si>
-  <si>
-    <t>Beat 2</t>
-  </si>
-  <si>
-    <t>BONSAVE OPTION</t>
-  </si>
-  <si>
-    <t>Custom hospital</t>
-  </si>
-  <si>
-    <t>Classic Saver (Delta)</t>
-  </si>
-  <si>
-    <t>Classic Smart Plan</t>
-  </si>
-  <si>
-    <t>Beané Booysen</t>
-  </si>
-  <si>
-    <t>Frederick Jacobus Joubert</t>
-  </si>
-  <si>
-    <t>Jolinda Steyn</t>
-  </si>
-  <si>
-    <t>Zandre Smit</t>
-  </si>
-  <si>
-    <t>Juan Strydom</t>
-  </si>
-  <si>
-    <t>Lelanie Swanepoel</t>
-  </si>
-  <si>
-    <t>Jaco Steyn</t>
-  </si>
-  <si>
-    <t>Gary Burnard</t>
-  </si>
-  <si>
-    <t>Chantè</t>
-  </si>
-  <si>
-    <t>Melissa koen</t>
-  </si>
-  <si>
-    <t>Phillippus Jacobus Volschenk</t>
-  </si>
-  <si>
-    <t>Hardus Potgieter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Theonette Joubert (Ouer) </t>
-  </si>
-  <si>
-    <t>0652086910</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Franco Joubert </t>
-  </si>
-  <si>
-    <t>0763309651</t>
-  </si>
-  <si>
-    <t>Sharna</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 083 581 9344</t>
-  </si>
-  <si>
-    <t>0767920837</t>
-  </si>
-  <si>
-    <t>Jolinda (ouer)</t>
-  </si>
-  <si>
-    <t>Jaco (ouer)</t>
-  </si>
-  <si>
-    <t>0716043786</t>
-  </si>
-  <si>
-    <t>Wynand (pa)</t>
-  </si>
-  <si>
-    <t>0826818810</t>
-  </si>
-  <si>
-    <t>Anita (ouma)</t>
-  </si>
-  <si>
-    <t>0827884560</t>
-  </si>
-  <si>
-    <t>Johan (oupa)</t>
-  </si>
-  <si>
-    <t>Emieke</t>
-  </si>
-  <si>
-    <t>Smit</t>
-  </si>
-  <si>
-    <t>Emile</t>
-  </si>
-  <si>
-    <t>Zandre(Ouer)</t>
-  </si>
-  <si>
-    <t>0682597142</t>
-  </si>
-  <si>
-    <t>Karen(Ouer)</t>
-  </si>
-  <si>
-    <t>0824982184</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 082 5602663</t>
-  </si>
-  <si>
-    <t>Elsje Swaters (Ouma)</t>
-  </si>
-  <si>
-    <t>Marcye(Ouer)</t>
-  </si>
-  <si>
-    <t>0736289802</t>
-  </si>
-  <si>
-    <t>JJ(Ouer)</t>
-  </si>
-  <si>
-    <t>0813264015</t>
-  </si>
-  <si>
-    <t>Juan-Mari</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Strydom</t>
-  </si>
-  <si>
-    <t>Lelanie (Ouer)</t>
-  </si>
-  <si>
-    <t>Hardus (Ouer)</t>
-  </si>
-  <si>
-    <t>0732921138</t>
-  </si>
-  <si>
-    <t>0837190631</t>
-  </si>
-  <si>
-    <t>Hendri (ouer)</t>
-  </si>
-  <si>
-    <t>Dewald Swart</t>
-  </si>
-  <si>
-    <t>0823428820</t>
-  </si>
-  <si>
-    <t>Andelien (ouer)</t>
-  </si>
-  <si>
-    <t>0823341343</t>
-  </si>
-  <si>
-    <t>0823247564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frikkie (oupa) </t>
-  </si>
-  <si>
-    <t>+27 (82) 551-9577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rochelle (ouer) </t>
-  </si>
-  <si>
-    <t>0734935157</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Gary (ouer)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0818277606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Janet (ouma) </t>
-  </si>
-  <si>
-    <t>0769708948</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0833841029</t>
-  </si>
-  <si>
-    <t>Chante (ouer)</t>
-  </si>
-  <si>
-    <t>Himne (Peetouer)</t>
-  </si>
-  <si>
-    <t>0783562003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melissa (parent) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">074 224 5661 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zander (parent) </t>
-  </si>
-  <si>
-    <t>0729293191</t>
-  </si>
-  <si>
-    <t>0723237879</t>
-  </si>
-  <si>
-    <t>Lehandre (Mamma)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0711078393</t>
-  </si>
-  <si>
-    <t>Flippie (Pappa)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0825511930</t>
-  </si>
-  <si>
-    <t>Jeanet (Tannie)</t>
-  </si>
-  <si>
-    <t>Talitha (Ouer)</t>
-  </si>
-  <si>
-    <t>0820644011</t>
-  </si>
-  <si>
-    <t>0726544695</t>
-  </si>
-  <si>
-    <t>0824214596</t>
-  </si>
-  <si>
-    <t>Annemarie Kruger (ouma)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0842193899</t>
-  </si>
-  <si>
-    <t>Danelle Smuts (tannie)</t>
-  </si>
-  <si>
-    <t>Admin Frassie</t>
-  </si>
-  <si>
-    <t>fritzlafras@gmail.com</t>
-  </si>
-  <si>
-    <t>admin</t>
-  </si>
-  <si>
-    <t>Greenhill Boetiek Kleuterskool</t>
-  </si>
-  <si>
-    <t>greenhill</t>
-  </si>
-  <si>
-    <t>himnefritz@gmail.com</t>
-  </si>
-  <si>
-    <t>Principal Himne</t>
+    <t>BonComprehensive</t>
+  </si>
+  <si>
+    <t>B77891</t>
+  </si>
+  <si>
+    <t>7902125101088</t>
+  </si>
+  <si>
+    <t>02</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="44" formatCode="_-&quot;R&quot;* #,##0.00_-;\-&quot;R&quot;* #,##0.00_-;_-&quot;R&quot;* &quot;-&quot;??_-;_-@_-"/>
-  </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -789,42 +489,8 @@
       <color rgb="FF102A43"/>
       <name val="Calibri"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF434343"/>
-      <name val="Roboto"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF434343"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="12">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -873,18 +539,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8F9FA"/>
+        <fgColor theme="6" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -914,84 +574,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFFFFFFF"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFFFFFFF"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF442F65"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFF8F9FA"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFF8F9FA"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFF8F9FA"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFF8F9FA"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFFFFFFF"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFFFFFFF"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFF8F9FA"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFF8F9FA"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFF8F9FA"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF442F65"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFF8F9FA"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -1060,93 +647,11 @@
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="10" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="11" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="10" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="11" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="10" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="11" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="1" fontId="13" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="13" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="10" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="2" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="3">
-    <cellStyle name="Currency" xfId="1" builtinId="4"/>
-    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1666,8 +1171,8 @@
       <c r="A5" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="11" t="s">
-        <v>228</v>
+      <c r="B5" s="24" t="s">
+        <v>5</v>
       </c>
       <c r="C5" s="12" t="s">
         <v>28</v>
@@ -1678,7 +1183,7 @@
         <v>29</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>229</v>
+        <v>5</v>
       </c>
       <c r="C6" s="14" t="s">
         <v>30</v>
@@ -1688,8 +1193,8 @@
       <c r="A7" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="B7" s="52" t="s">
-        <v>230</v>
+      <c r="B7" s="24" t="s">
+        <v>5</v>
       </c>
       <c r="C7" s="12" t="s">
         <v>32</v>
@@ -1699,8 +1204,8 @@
       <c r="A8" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="B8" s="11" t="s">
-        <v>231</v>
+      <c r="B8" s="24" t="s">
+        <v>5</v>
       </c>
       <c r="C8" s="14" t="s">
         <v>34</v>
@@ -1799,9 +1304,6 @@
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:C2"/>
   </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="B7" r:id="rId1" xr:uid="{32BCC219-75AD-4D41-BD75-F6921CEBAED8}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
@@ -1868,104 +1370,224 @@
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
-        <v>225</v>
-      </c>
-      <c r="B6" s="51" t="s">
-        <v>226</v>
+        <v>60</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>61</v>
       </c>
       <c r="C6" s="15" t="s">
         <v>36</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>227</v>
+        <v>62</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>109</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="16"/>
-      <c r="B7" s="16"/>
-      <c r="C7" s="16"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
+      <c r="A7" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="15"/>
-      <c r="B8" s="15"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
+      <c r="A8" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="16"/>
-      <c r="B9" s="16"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
+      <c r="A9" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="16"/>
-      <c r="B10" s="16"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
+      <c r="A10" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="E10" s="16" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="16"/>
-      <c r="B11" s="16"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
+      <c r="A11" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="E11" s="16" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="16"/>
-      <c r="B12" s="16"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
+      <c r="A12" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="13" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="16"/>
-      <c r="B13" s="16"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
+      <c r="A13" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="E13" s="16" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="16"/>
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
+      <c r="A14" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="E14" s="16" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="15" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="16"/>
-      <c r="B15" s="16"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
+      <c r="A15" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="E15" s="16" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="16" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="16"/>
-      <c r="B16" s="16"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
+      <c r="A16" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="17" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="16"/>
-      <c r="B17" s="16"/>
-      <c r="C17" s="16"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
+      <c r="A17" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="D17" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="E17" s="16" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="18" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="16"/>
-      <c r="B18" s="16"/>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
+      <c r="A18" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="E18" s="16" t="s">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1973,9 +1595,6 @@
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A3:E3"/>
   </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="B6" r:id="rId1" xr:uid="{25BE33D0-17B9-4ED5-83DA-12579D17D4E2}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
@@ -1986,7 +1605,7 @@
   <sheetPr>
     <tabColor rgb="FFFFB703"/>
   </sheetPr>
-  <dimension ref="A1:U38"/>
+  <dimension ref="A1:V38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="18" customWidth="1"/>
@@ -1996,21 +1615,22 @@
     <col min="8" max="8" width="30" customWidth="1"/>
     <col min="9" max="9" width="24" customWidth="1"/>
     <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="24" customWidth="1"/>
-    <col min="12" max="12" width="18" customWidth="1"/>
-    <col min="13" max="13" width="24" customWidth="1"/>
-    <col min="14" max="14" width="18" customWidth="1"/>
-    <col min="15" max="16" width="20" customWidth="1"/>
-    <col min="17" max="17" width="18" customWidth="1"/>
-    <col min="18" max="18" width="25.85546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="24" customWidth="1"/>
-    <col min="21" max="21" width="22" customWidth="1"/>
+    <col min="11" max="11" width="30" customWidth="1"/>
+    <col min="12" max="12" width="24" customWidth="1"/>
+    <col min="13" max="13" width="18" customWidth="1"/>
+    <col min="14" max="14" width="24" customWidth="1"/>
+    <col min="15" max="15" width="18" customWidth="1"/>
+    <col min="16" max="17" width="20" customWidth="1"/>
+    <col min="18" max="18" width="18" customWidth="1"/>
+    <col min="19" max="19" width="24" customWidth="1"/>
+    <col min="20" max="20" width="20" customWidth="1"/>
+    <col min="21" max="21" width="24" customWidth="1"/>
+    <col min="22" max="22" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="B1" s="23"/>
       <c r="C1" s="23"/>
@@ -2032,10 +1652,11 @@
       <c r="S1" s="23"/>
       <c r="T1" s="23"/>
       <c r="U1" s="23"/>
-    </row>
-    <row r="2" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V1" s="23"/>
+    </row>
+    <row r="2" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="B2" s="20"/>
       <c r="C2" s="20"/>
@@ -2057,10 +1678,11 @@
       <c r="S2" s="20"/>
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
-    </row>
-    <row r="3" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V2" s="20"/>
+    </row>
+    <row r="3" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="B3" s="22"/>
       <c r="C3" s="22"/>
@@ -2082,977 +1704,1029 @@
       <c r="S3" s="22"/>
       <c r="T3" s="22"/>
       <c r="U3" s="22"/>
-    </row>
-    <row r="5" spans="1:21" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V3" s="22"/>
+    </row>
+    <row r="5" spans="1:22" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="E5" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="F5" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="G5" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="H5" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="I5" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="J5" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="K5" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="L5" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="M5" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="N5" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="O5" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="P5" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q5" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="R5" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="S5" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="T5" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="U5" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="V5" s="18" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="D6" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="B5" s="18" t="s">
-        <v>64</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="D5" s="18" t="s">
+      <c r="E6" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="F6" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="G6" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="H6" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="I6" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="J6" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="K6" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="L6" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="M6" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="N6" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="O6" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="P6" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q6" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="R6" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="S6" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="T6" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="U6" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="V6" s="15" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="H7" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="I7" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="J7" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="K7" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="L7" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="M7" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="N7" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="O7" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="P7" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q7" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="R7" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="S7" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="T7" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="U7" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="V7" s="16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D8" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="E5" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="F5" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="G5" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="H5" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="I5" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="J5" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="K5" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="L5" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="M5" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="N5" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="O5" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="P5" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q5" s="18" t="s">
-        <v>79</v>
-      </c>
-      <c r="R5" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="S5" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="T5" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="U5" s="18" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="41">
-        <v>2505160523086</v>
-      </c>
-      <c r="B6" s="24" t="s">
-        <v>87</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="D6" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="E6" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="F6" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="G6" s="32" t="s">
+      <c r="E8" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="G8" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="H8" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="I8" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="J8" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="K8" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="L8" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="M8" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="H6" s="24" t="s">
-        <v>111</v>
-      </c>
-      <c r="I6" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="J6" s="32" t="s">
-        <v>124</v>
-      </c>
-      <c r="K6" s="15" t="s">
+      <c r="N8" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="O8" s="15" t="s">
         <v>127</v>
       </c>
-      <c r="L6" s="32" t="s">
-        <v>126</v>
-      </c>
-      <c r="M6" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="N6" s="32" t="s">
-        <v>5</v>
-      </c>
-      <c r="O6" s="24" t="s">
+      <c r="P8" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="P6" s="24" t="s">
-        <v>133</v>
-      </c>
-      <c r="Q6" s="28">
-        <v>55201039894</v>
-      </c>
-      <c r="R6" s="24" t="s">
-        <v>144</v>
-      </c>
-      <c r="S6" s="34">
-        <v>9203170118088</v>
-      </c>
-      <c r="T6" s="24">
-        <v>2</v>
-      </c>
-      <c r="U6" s="15" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="42">
-        <v>2204025282084</v>
-      </c>
-      <c r="B7" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="C7" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="D7" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="E7" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="F7" s="40" t="s">
-        <v>156</v>
-      </c>
-      <c r="G7" s="46" t="s">
-        <v>157</v>
-      </c>
-      <c r="H7" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="I7" s="40" t="s">
-        <v>158</v>
-      </c>
-      <c r="J7" s="46" t="s">
-        <v>159</v>
-      </c>
-      <c r="K7" s="16" t="s">
-        <v>160</v>
-      </c>
-      <c r="L7" s="33" t="s">
-        <v>161</v>
-      </c>
-      <c r="M7" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="N7" s="33" t="s">
-        <v>5</v>
-      </c>
-      <c r="O7" s="25" t="s">
-        <v>84</v>
-      </c>
-      <c r="P7" s="25" t="s">
-        <v>134</v>
-      </c>
-      <c r="Q7" s="29">
-        <v>424204550</v>
-      </c>
-      <c r="R7" s="25" t="s">
-        <v>145</v>
-      </c>
-      <c r="S7" s="35">
-        <v>8801165150080</v>
-      </c>
-      <c r="T7" s="25">
-        <v>3</v>
-      </c>
-      <c r="U7" s="16" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="43">
-        <v>2201030584082</v>
-      </c>
-      <c r="B8" s="26" t="s">
-        <v>91</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="E8" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="F8" s="15" t="s">
-        <v>163</v>
-      </c>
-      <c r="G8" s="32" t="s">
-        <v>162</v>
-      </c>
-      <c r="H8" s="26" t="s">
-        <v>113</v>
-      </c>
-      <c r="I8" s="15" t="s">
-        <v>166</v>
-      </c>
-      <c r="J8" s="32" t="s">
-        <v>165</v>
-      </c>
-      <c r="K8" s="15" t="s">
-        <v>168</v>
-      </c>
-      <c r="L8" s="32" t="s">
-        <v>167</v>
-      </c>
-      <c r="M8" s="15" t="s">
-        <v>170</v>
-      </c>
-      <c r="N8" s="32" t="s">
-        <v>169</v>
-      </c>
-      <c r="O8" s="26" t="s">
+      <c r="Q8" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="P8" s="26" t="s">
-        <v>135</v>
-      </c>
-      <c r="Q8" s="30">
-        <v>912589175</v>
-      </c>
-      <c r="R8" s="26" t="s">
-        <v>146</v>
-      </c>
-      <c r="S8" s="36">
-        <v>9401270325088</v>
-      </c>
-      <c r="T8" s="26">
-        <v>3</v>
+      <c r="R8" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="S8" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="T8" s="15" t="s">
+        <v>131</v>
       </c>
       <c r="U8" s="15" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="42">
-        <v>2503065359086</v>
-      </c>
-      <c r="B9" s="25" t="s">
-        <v>93</v>
+        <v>132</v>
+      </c>
+      <c r="V8" s="15" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>5</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="D9" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="E9" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="F9" s="15" t="s">
-        <v>163</v>
-      </c>
-      <c r="G9" s="32" t="s">
-        <v>162</v>
-      </c>
-      <c r="H9" s="25" t="s">
-        <v>113</v>
-      </c>
-      <c r="I9" s="15" t="s">
-        <v>166</v>
-      </c>
-      <c r="J9" s="32" t="s">
-        <v>165</v>
-      </c>
-      <c r="K9" s="15" t="s">
-        <v>168</v>
-      </c>
-      <c r="L9" s="32" t="s">
-        <v>167</v>
-      </c>
-      <c r="M9" s="15" t="s">
-        <v>170</v>
-      </c>
-      <c r="N9" s="32" t="s">
-        <v>169</v>
-      </c>
-      <c r="O9" s="25" t="s">
-        <v>129</v>
-      </c>
-      <c r="P9" s="25" t="s">
-        <v>135</v>
-      </c>
-      <c r="Q9" s="29">
-        <v>912589175</v>
-      </c>
-      <c r="R9" s="25" t="s">
-        <v>146</v>
-      </c>
-      <c r="S9" s="37">
-        <v>9401270325088</v>
-      </c>
-      <c r="T9" s="25">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="G9" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="H9" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="I9" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="J9" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="N9" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="O9" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="P9" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q9" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="R9" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="S9" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="T9" s="16" t="s">
+        <v>5</v>
       </c>
       <c r="U9" s="16" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="44">
-        <v>2211156377088</v>
-      </c>
-      <c r="B10" s="26" t="s">
-        <v>173</v>
+      <c r="V9" s="16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>5</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>172</v>
-      </c>
-      <c r="D10" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="E10" s="15" t="s">
-        <v>94</v>
+        <v>5</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="E10" s="16" t="s">
+        <v>5</v>
       </c>
       <c r="F10" s="16" t="s">
-        <v>174</v>
-      </c>
-      <c r="G10" s="33" t="s">
-        <v>175</v>
-      </c>
-      <c r="H10" s="26" t="s">
-        <v>114</v>
+        <v>5</v>
+      </c>
+      <c r="G10" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="H10" s="16" t="s">
+        <v>5</v>
       </c>
       <c r="I10" s="16" t="s">
-        <v>176</v>
-      </c>
-      <c r="J10" s="46" t="s">
-        <v>177</v>
+        <v>5</v>
+      </c>
+      <c r="J10" s="16" t="s">
+        <v>5</v>
       </c>
       <c r="K10" s="16" t="s">
-        <v>179</v>
-      </c>
-      <c r="L10" s="50" t="s">
-        <v>178</v>
+        <v>5</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>5</v>
       </c>
       <c r="M10" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="N10" s="33" t="s">
-        <v>5</v>
-      </c>
-      <c r="O10" s="26" t="s">
-        <v>84</v>
-      </c>
-      <c r="P10" s="26" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q10" s="30">
-        <v>754178400</v>
-      </c>
-      <c r="R10" s="26" t="s">
-        <v>147</v>
-      </c>
-      <c r="S10" s="38">
-        <v>9104075064080</v>
-      </c>
-      <c r="T10" s="26">
-        <v>2</v>
+      <c r="N10" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="O10" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="P10" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q10" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="R10" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="S10" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="T10" s="16" t="s">
+        <v>5</v>
       </c>
       <c r="U10" s="16" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="47">
-        <v>2407120307082</v>
-      </c>
-      <c r="B11" s="48" t="s">
-        <v>171</v>
+      <c r="V10" s="16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>5</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>172</v>
-      </c>
-      <c r="D11" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="E11" s="15" t="s">
-        <v>94</v>
+        <v>5</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="E11" s="16" t="s">
+        <v>5</v>
       </c>
       <c r="F11" s="16" t="s">
-        <v>174</v>
-      </c>
-      <c r="G11" s="33" t="s">
-        <v>175</v>
-      </c>
-      <c r="H11" s="40" t="s">
-        <v>114</v>
+        <v>5</v>
+      </c>
+      <c r="G11" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="H11" s="16" t="s">
+        <v>5</v>
       </c>
       <c r="I11" s="16" t="s">
-        <v>176</v>
-      </c>
-      <c r="J11" s="46" t="s">
-        <v>177</v>
+        <v>5</v>
+      </c>
+      <c r="J11" s="16" t="s">
+        <v>5</v>
       </c>
       <c r="K11" s="16" t="s">
-        <v>179</v>
-      </c>
-      <c r="L11" s="50" t="s">
-        <v>178</v>
-      </c>
-      <c r="M11" s="16"/>
-      <c r="N11" s="33"/>
-      <c r="O11" s="26" t="s">
-        <v>84</v>
-      </c>
-      <c r="P11" s="26" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q11" s="30">
-        <v>754178400</v>
-      </c>
-      <c r="R11" s="26" t="s">
-        <v>147</v>
-      </c>
-      <c r="S11" s="49">
-        <v>9104075064080</v>
-      </c>
-      <c r="T11" s="48">
-        <v>3</v>
-      </c>
-      <c r="U11" s="16"/>
-    </row>
-    <row r="12" spans="1:21" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="43">
-        <v>2406300437081</v>
-      </c>
-      <c r="B12" s="26" t="s">
-        <v>184</v>
+        <v>5</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="N11" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="O11" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="P11" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q11" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="R11" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="S11" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="T11" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="U11" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="V11" s="16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>5</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>185</v>
-      </c>
-      <c r="D12" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="E12" s="15" t="s">
-        <v>94</v>
+        <v>5</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>5</v>
       </c>
       <c r="F12" s="16" t="s">
-        <v>180</v>
-      </c>
-      <c r="G12" s="33" t="s">
-        <v>181</v>
-      </c>
-      <c r="H12" s="26" t="s">
-        <v>115</v>
+        <v>5</v>
+      </c>
+      <c r="G12" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="H12" s="16" t="s">
+        <v>5</v>
       </c>
       <c r="I12" s="16" t="s">
-        <v>182</v>
-      </c>
-      <c r="J12" s="33" t="s">
-        <v>183</v>
+        <v>5</v>
+      </c>
+      <c r="J12" s="16" t="s">
+        <v>5</v>
       </c>
       <c r="K12" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="L12" s="33" t="s">
+      <c r="L12" s="16" t="s">
         <v>5</v>
       </c>
       <c r="M12" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="N12" s="33" t="s">
-        <v>5</v>
-      </c>
-      <c r="O12" s="26" t="s">
-        <v>130</v>
-      </c>
-      <c r="P12" s="26" t="s">
-        <v>135</v>
-      </c>
-      <c r="Q12" s="30">
-        <v>916649819</v>
-      </c>
-      <c r="R12" s="26" t="s">
-        <v>148</v>
-      </c>
-      <c r="S12" s="38">
-        <v>9211275050080</v>
-      </c>
-      <c r="T12" s="26">
-        <v>3</v>
+      <c r="N12" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="O12" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="P12" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q12" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="R12" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="S12" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="T12" s="16" t="s">
+        <v>5</v>
       </c>
       <c r="U12" s="16" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="42">
-        <v>2312015507087</v>
-      </c>
-      <c r="B13" s="25" t="s">
-        <v>106</v>
+      <c r="V12" s="16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>5</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>107</v>
-      </c>
-      <c r="D13" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="E13" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="F13" s="40" t="s">
-        <v>186</v>
-      </c>
-      <c r="G13" s="46" t="s">
-        <v>188</v>
-      </c>
-      <c r="H13" s="25" t="s">
-        <v>116</v>
+        <v>5</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="E13" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="F13" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="G13" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="H13" s="16" t="s">
+        <v>5</v>
       </c>
       <c r="I13" s="16" t="s">
-        <v>190</v>
-      </c>
-      <c r="J13" s="33" t="s">
-        <v>189</v>
+        <v>5</v>
+      </c>
+      <c r="J13" s="16" t="s">
+        <v>5</v>
       </c>
       <c r="K13" s="16" t="s">
-        <v>191</v>
-      </c>
-      <c r="L13" s="33" t="s">
-        <v>192</v>
+        <v>5</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>5</v>
       </c>
       <c r="M13" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="N13" s="33" t="s">
-        <v>5</v>
-      </c>
-      <c r="O13" s="25" t="s">
-        <v>131</v>
-      </c>
-      <c r="P13" s="25" t="s">
-        <v>137</v>
-      </c>
-      <c r="Q13" s="29">
-        <v>7165897</v>
-      </c>
-      <c r="R13" s="25" t="s">
-        <v>149</v>
-      </c>
-      <c r="S13" s="35">
-        <v>8407220010085</v>
-      </c>
-      <c r="T13" s="29">
-        <v>2</v>
+      <c r="N13" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="O13" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="P13" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q13" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="R13" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="S13" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="T13" s="16" t="s">
+        <v>5</v>
       </c>
       <c r="U13" s="16" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="43">
-        <v>2306266148088</v>
-      </c>
-      <c r="B14" s="26" t="s">
-        <v>105</v>
+      <c r="V13" s="16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>5</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="D14" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="E14" s="15" t="s">
-        <v>94</v>
+        <v>5</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="16" t="s">
+        <v>5</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>193</v>
-      </c>
-      <c r="G14" s="33" t="s">
-        <v>194</v>
-      </c>
-      <c r="H14" s="26" t="s">
-        <v>117</v>
+        <v>5</v>
+      </c>
+      <c r="G14" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" s="16" t="s">
+        <v>5</v>
       </c>
       <c r="I14" s="16" t="s">
-        <v>164</v>
-      </c>
-      <c r="J14" s="33" t="s">
-        <v>195</v>
+        <v>5</v>
+      </c>
+      <c r="J14" s="16" t="s">
+        <v>5</v>
       </c>
       <c r="K14" s="16" t="s">
-        <v>196</v>
-      </c>
-      <c r="L14" s="33" t="s">
-        <v>197</v>
+        <v>5</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>5</v>
       </c>
       <c r="M14" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="N14" s="33" t="s">
-        <v>5</v>
-      </c>
-      <c r="O14" s="26" t="s">
-        <v>131</v>
-      </c>
-      <c r="P14" s="26" t="s">
-        <v>138</v>
-      </c>
-      <c r="Q14" s="30">
-        <v>7693818</v>
-      </c>
-      <c r="R14" s="26" t="s">
-        <v>150</v>
-      </c>
-      <c r="S14" s="38">
-        <v>8504275017088</v>
-      </c>
-      <c r="T14" s="30">
-        <v>4</v>
+      <c r="N14" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="O14" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="P14" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q14" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="R14" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="S14" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="T14" s="16" t="s">
+        <v>5</v>
       </c>
       <c r="U14" s="16" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="42">
-        <v>2508015620081</v>
-      </c>
-      <c r="B15" s="25" t="s">
-        <v>103</v>
+      <c r="V14" s="16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>5</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="D15" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="E15" s="15" t="s">
-        <v>94</v>
+        <v>5</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" s="16" t="s">
+        <v>5</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>198</v>
-      </c>
-      <c r="G15" s="33" t="s">
-        <v>199</v>
-      </c>
-      <c r="H15" s="25" t="s">
-        <v>118</v>
+        <v>5</v>
+      </c>
+      <c r="G15" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="H15" s="16" t="s">
+        <v>5</v>
       </c>
       <c r="I15" s="16" t="s">
-        <v>200</v>
-      </c>
-      <c r="J15" s="33" t="s">
-        <v>201</v>
+        <v>5</v>
+      </c>
+      <c r="J15" s="16" t="s">
+        <v>5</v>
       </c>
       <c r="K15" s="16" t="s">
-        <v>202</v>
-      </c>
-      <c r="L15" s="33" t="s">
-        <v>203</v>
+        <v>5</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>5</v>
       </c>
       <c r="M15" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="N15" s="33" t="s">
-        <v>5</v>
-      </c>
-      <c r="O15" s="25" t="s">
-        <v>132</v>
-      </c>
-      <c r="P15" s="25" t="s">
-        <v>139</v>
-      </c>
-      <c r="Q15" s="29">
-        <v>198477457</v>
-      </c>
-      <c r="R15" s="25" t="s">
-        <v>151</v>
-      </c>
-      <c r="S15" s="35">
-        <v>9105025024082</v>
-      </c>
-      <c r="T15" s="25">
-        <v>2</v>
+      <c r="N15" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="O15" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="P15" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q15" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="R15" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="S15" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="T15" s="16" t="s">
+        <v>5</v>
       </c>
       <c r="U15" s="16" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="43">
-        <v>2307215736080</v>
-      </c>
-      <c r="B16" s="26" t="s">
-        <v>101</v>
+      <c r="V15" s="16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>5</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>102</v>
-      </c>
-      <c r="D16" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="E16" s="15" t="s">
-        <v>94</v>
+        <v>5</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>5</v>
       </c>
       <c r="F16" s="16" t="s">
-        <v>205</v>
-      </c>
-      <c r="G16" s="33" t="s">
-        <v>204</v>
-      </c>
-      <c r="H16" s="26" t="s">
-        <v>119</v>
+        <v>5</v>
+      </c>
+      <c r="G16" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="H16" s="16" t="s">
+        <v>5</v>
       </c>
       <c r="I16" s="16" t="s">
-        <v>206</v>
-      </c>
-      <c r="J16" s="33" t="s">
-        <v>207</v>
+        <v>5</v>
+      </c>
+      <c r="J16" s="16" t="s">
+        <v>5</v>
       </c>
       <c r="K16" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="L16" s="33" t="s">
+      <c r="L16" s="16" t="s">
         <v>5</v>
       </c>
       <c r="M16" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="N16" s="33" t="s">
-        <v>5</v>
-      </c>
-      <c r="O16" s="26" t="s">
-        <v>86</v>
-      </c>
-      <c r="P16" s="26" t="s">
-        <v>140</v>
-      </c>
-      <c r="Q16" s="30">
-        <v>24004278285</v>
-      </c>
-      <c r="R16" s="26" t="s">
-        <v>152</v>
-      </c>
-      <c r="S16" s="38">
-        <v>9709270112086</v>
-      </c>
-      <c r="T16" s="26">
-        <v>3</v>
+      <c r="N16" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="O16" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="P16" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q16" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="R16" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="S16" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="T16" s="16" t="s">
+        <v>5</v>
       </c>
       <c r="U16" s="16" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="17" spans="1:21" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="42">
-        <v>2301270371081</v>
-      </c>
-      <c r="B17" s="25" t="s">
-        <v>99</v>
+      <c r="V16" s="16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>5</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>100</v>
-      </c>
-      <c r="D17" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="E17" s="15" t="s">
-        <v>94</v>
+        <v>5</v>
+      </c>
+      <c r="D17" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="E17" s="16" t="s">
+        <v>5</v>
       </c>
       <c r="F17" s="16" t="s">
-        <v>208</v>
-      </c>
-      <c r="G17" s="33" t="s">
-        <v>209</v>
-      </c>
-      <c r="H17" s="25" t="s">
-        <v>120</v>
+        <v>5</v>
+      </c>
+      <c r="G17" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="H17" s="16" t="s">
+        <v>5</v>
       </c>
       <c r="I17" s="16" t="s">
-        <v>210</v>
-      </c>
-      <c r="J17" s="33" t="s">
-        <v>211</v>
+        <v>5</v>
+      </c>
+      <c r="J17" s="16" t="s">
+        <v>5</v>
       </c>
       <c r="K17" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="L17" s="33" t="s">
+      <c r="L17" s="16" t="s">
         <v>5</v>
       </c>
       <c r="M17" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="N17" s="33" t="s">
-        <v>5</v>
-      </c>
-      <c r="O17" s="25" t="s">
-        <v>130</v>
-      </c>
-      <c r="P17" s="25" t="s">
-        <v>141</v>
-      </c>
-      <c r="Q17" s="29">
-        <v>915065195</v>
-      </c>
-      <c r="R17" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="S17" s="35">
-        <v>9206100035082</v>
-      </c>
-      <c r="T17" s="25">
-        <v>2</v>
+      <c r="N17" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="O17" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="P17" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q17" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="R17" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="S17" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="T17" s="16" t="s">
+        <v>5</v>
       </c>
       <c r="U17" s="16" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="18" spans="1:21" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="44" t="s">
-        <v>108</v>
-      </c>
-      <c r="B18" s="26" t="s">
-        <v>97</v>
+      <c r="V17" s="16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>5</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="D18" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="E18" s="15" t="s">
-        <v>94</v>
+        <v>5</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="E18" s="16" t="s">
+        <v>5</v>
       </c>
       <c r="F18" s="16" t="s">
-        <v>213</v>
-      </c>
-      <c r="G18" s="33" t="s">
-        <v>212</v>
-      </c>
-      <c r="H18" s="26" t="s">
-        <v>121</v>
+        <v>5</v>
+      </c>
+      <c r="G18" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="H18" s="16" t="s">
+        <v>5</v>
       </c>
       <c r="I18" s="16" t="s">
-        <v>215</v>
-      </c>
-      <c r="J18" s="33" t="s">
-        <v>214</v>
+        <v>5</v>
+      </c>
+      <c r="J18" s="16" t="s">
+        <v>5</v>
       </c>
       <c r="K18" s="16" t="s">
-        <v>217</v>
-      </c>
-      <c r="L18" s="33" t="s">
-        <v>216</v>
+        <v>5</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>5</v>
       </c>
       <c r="M18" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="N18" s="33" t="s">
-        <v>5</v>
-      </c>
-      <c r="O18" s="26" t="s">
-        <v>84</v>
-      </c>
-      <c r="P18" s="26" t="s">
-        <v>142</v>
-      </c>
-      <c r="Q18" s="30">
-        <v>651706560</v>
-      </c>
-      <c r="R18" s="26" t="s">
-        <v>154</v>
-      </c>
-      <c r="S18" s="38">
-        <v>9008225010085</v>
-      </c>
-      <c r="T18" s="26">
-        <v>3</v>
+      <c r="N18" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="O18" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="P18" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q18" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="R18" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="S18" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="T18" s="16" t="s">
+        <v>5</v>
       </c>
       <c r="U18" s="16" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="19" spans="1:21" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="45">
-        <v>2109015397083</v>
-      </c>
-      <c r="B19" s="27" t="s">
-        <v>95</v>
+      <c r="V18" s="16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>5</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="D19" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="E19" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="F19" s="40" t="s">
-        <v>218</v>
-      </c>
-      <c r="G19" s="46" t="s">
-        <v>219</v>
-      </c>
-      <c r="H19" s="27" t="s">
-        <v>122</v>
-      </c>
-      <c r="I19" s="40" t="s">
-        <v>187</v>
-      </c>
-      <c r="J19" s="46" t="s">
-        <v>220</v>
+        <v>5</v>
+      </c>
+      <c r="D19" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="E19" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="F19" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="G19" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="H19" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="I19" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="J19" s="16" t="s">
+        <v>5</v>
       </c>
       <c r="K19" s="16" t="s">
-        <v>222</v>
-      </c>
-      <c r="L19" s="33" t="s">
-        <v>221</v>
+        <v>5</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>5</v>
       </c>
       <c r="M19" s="16" t="s">
-        <v>224</v>
-      </c>
-      <c r="N19" s="33" t="s">
-        <v>223</v>
-      </c>
-      <c r="O19" s="27" t="s">
-        <v>84</v>
-      </c>
-      <c r="P19" s="27" t="s">
-        <v>143</v>
-      </c>
-      <c r="Q19" s="31">
-        <v>934646670</v>
-      </c>
-      <c r="R19" s="27" t="s">
-        <v>155</v>
-      </c>
-      <c r="S19" s="39">
-        <v>8106165203081</v>
-      </c>
-      <c r="T19" s="27">
+        <v>5</v>
+      </c>
+      <c r="N19" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="O19" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="P19" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q19" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="R19" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="S19" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="T19" s="16" t="s">
         <v>5</v>
       </c>
       <c r="U19" s="16" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="20" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V19" s="16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
         <v>5</v>
       </c>
@@ -3077,20 +2751,22 @@
       <c r="H20" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="I20" s="16"/>
-      <c r="J20" s="33" t="s">
+      <c r="I20" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="J20" s="16" t="s">
         <v>5</v>
       </c>
       <c r="K20" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="L20" s="33" t="s">
+      <c r="L20" s="16" t="s">
         <v>5</v>
       </c>
       <c r="M20" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="N20" s="33" t="s">
+      <c r="N20" s="16" t="s">
         <v>5</v>
       </c>
       <c r="O20" s="16" t="s">
@@ -3105,7 +2781,7 @@
       <c r="R20" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="S20" s="33" t="s">
+      <c r="S20" s="16" t="s">
         <v>5</v>
       </c>
       <c r="T20" s="16" t="s">
@@ -3114,8 +2790,11 @@
       <c r="U20" s="16" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="21" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V20" s="16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
         <v>5</v>
       </c>
@@ -3143,19 +2822,19 @@
       <c r="I21" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="J21" s="33" t="s">
+      <c r="J21" s="16" t="s">
         <v>5</v>
       </c>
       <c r="K21" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="L21" s="33" t="s">
+      <c r="L21" s="16" t="s">
         <v>5</v>
       </c>
       <c r="M21" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="N21" s="33" t="s">
+      <c r="N21" s="16" t="s">
         <v>5</v>
       </c>
       <c r="O21" s="16" t="s">
@@ -3170,7 +2849,7 @@
       <c r="R21" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="S21" s="33" t="s">
+      <c r="S21" s="16" t="s">
         <v>5</v>
       </c>
       <c r="T21" s="16" t="s">
@@ -3179,8 +2858,11 @@
       <c r="U21" s="16" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V21" s="16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="s">
         <v>5</v>
       </c>
@@ -3208,19 +2890,19 @@
       <c r="I22" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="J22" s="33" t="s">
+      <c r="J22" s="16" t="s">
         <v>5</v>
       </c>
       <c r="K22" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="L22" s="33" t="s">
+      <c r="L22" s="16" t="s">
         <v>5</v>
       </c>
       <c r="M22" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="N22" s="33" t="s">
+      <c r="N22" s="16" t="s">
         <v>5</v>
       </c>
       <c r="O22" s="16" t="s">
@@ -3235,7 +2917,7 @@
       <c r="R22" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="S22" s="33" t="s">
+      <c r="S22" s="16" t="s">
         <v>5</v>
       </c>
       <c r="T22" s="16" t="s">
@@ -3244,8 +2926,11 @@
       <c r="U22" s="16" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V22" s="16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="16" t="s">
         <v>5</v>
       </c>
@@ -3273,19 +2958,19 @@
       <c r="I23" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="J23" s="33" t="s">
+      <c r="J23" s="16" t="s">
         <v>5</v>
       </c>
       <c r="K23" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="L23" s="33" t="s">
+      <c r="L23" s="16" t="s">
         <v>5</v>
       </c>
       <c r="M23" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="N23" s="33" t="s">
+      <c r="N23" s="16" t="s">
         <v>5</v>
       </c>
       <c r="O23" s="16" t="s">
@@ -3300,7 +2985,7 @@
       <c r="R23" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="S23" s="33" t="s">
+      <c r="S23" s="16" t="s">
         <v>5</v>
       </c>
       <c r="T23" s="16" t="s">
@@ -3309,8 +2994,11 @@
       <c r="U23" s="16" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="24" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V23" s="16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
         <v>5</v>
       </c>
@@ -3338,19 +3026,19 @@
       <c r="I24" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="J24" s="33" t="s">
+      <c r="J24" s="16" t="s">
         <v>5</v>
       </c>
       <c r="K24" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="L24" s="33" t="s">
+      <c r="L24" s="16" t="s">
         <v>5</v>
       </c>
       <c r="M24" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="N24" s="33" t="s">
+      <c r="N24" s="16" t="s">
         <v>5</v>
       </c>
       <c r="O24" s="16" t="s">
@@ -3365,7 +3053,7 @@
       <c r="R24" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="S24" s="33" t="s">
+      <c r="S24" s="16" t="s">
         <v>5</v>
       </c>
       <c r="T24" s="16" t="s">
@@ -3374,8 +3062,11 @@
       <c r="U24" s="16" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="25" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V24" s="16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="16" t="s">
         <v>5</v>
       </c>
@@ -3403,19 +3094,19 @@
       <c r="I25" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="J25" s="33" t="s">
+      <c r="J25" s="16" t="s">
         <v>5</v>
       </c>
       <c r="K25" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="L25" s="33" t="s">
+      <c r="L25" s="16" t="s">
         <v>5</v>
       </c>
       <c r="M25" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="N25" s="33" t="s">
+      <c r="N25" s="16" t="s">
         <v>5</v>
       </c>
       <c r="O25" s="16" t="s">
@@ -3430,7 +3121,7 @@
       <c r="R25" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="S25" s="33" t="s">
+      <c r="S25" s="16" t="s">
         <v>5</v>
       </c>
       <c r="T25" s="16" t="s">
@@ -3439,8 +3130,11 @@
       <c r="U25" s="16" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="26" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V25" s="16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="16" t="s">
         <v>5</v>
       </c>
@@ -3480,7 +3174,7 @@
       <c r="M26" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="N26" s="33" t="s">
+      <c r="N26" s="16" t="s">
         <v>5</v>
       </c>
       <c r="O26" s="16" t="s">
@@ -3504,8 +3198,11 @@
       <c r="U26" s="16" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="27" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V26" s="16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="16" t="s">
         <v>5</v>
       </c>
@@ -3569,8 +3266,11 @@
       <c r="U27" s="16" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="28" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V27" s="16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="16" t="s">
         <v>5</v>
       </c>
@@ -3634,8 +3334,11 @@
       <c r="U28" s="16" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="29" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V28" s="16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="16" t="s">
         <v>5</v>
       </c>
@@ -3699,8 +3402,11 @@
       <c r="U29" s="16" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V29" s="16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
         <v>5</v>
       </c>
@@ -3764,8 +3470,11 @@
       <c r="U30" s="16" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="31" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V30" s="16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="16" t="s">
         <v>5</v>
       </c>
@@ -3829,8 +3538,11 @@
       <c r="U31" s="16" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="32" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V31" s="16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="16" t="s">
         <v>5</v>
       </c>
@@ -3894,8 +3606,11 @@
       <c r="U32" s="16" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="33" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V32" s="16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="16" t="s">
         <v>5</v>
       </c>
@@ -3959,8 +3674,11 @@
       <c r="U33" s="16" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="34" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V33" s="16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="16" t="s">
         <v>5</v>
       </c>
@@ -4024,8 +3742,11 @@
       <c r="U34" s="16" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="35" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V34" s="16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="16" t="s">
         <v>5</v>
       </c>
@@ -4089,8 +3810,11 @@
       <c r="U35" s="16" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="36" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V35" s="16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="16" t="s">
         <v>5</v>
       </c>
@@ -4154,8 +3878,11 @@
       <c r="U36" s="16" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="37" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V36" s="16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="16" t="s">
         <v>5</v>
       </c>
@@ -4219,8 +3946,11 @@
       <c r="U37" s="16" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="38" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V37" s="16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="16" t="s">
         <v>5</v>
       </c>
@@ -4282,14 +4012,17 @@
         <v>5</v>
       </c>
       <c r="U38" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="V38" s="16" t="s">
         <v>5</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1:U1"/>
-    <mergeCell ref="A2:U2"/>
-    <mergeCell ref="A3:U3"/>
+    <mergeCell ref="A1:V1"/>
+    <mergeCell ref="A2:V2"/>
+    <mergeCell ref="A3:V3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
